--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/121.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/121.xlsx
@@ -426,13 +426,13 @@
         <v>-7.390557895530767</v>
       </c>
       <c r="E2">
-        <v>-23.11039896070013</v>
+        <v>-26.79589300336865</v>
       </c>
       <c r="F2">
-        <v>-2.641037549018615</v>
+        <v>-2.506677184651938</v>
       </c>
       <c r="G2">
-        <v>-11.71771350291963</v>
+        <v>-14.5629486244641</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.384809531232174</v>
       </c>
       <c r="E3">
-        <v>-23.52928733488365</v>
+        <v>-26.2227195197438</v>
       </c>
       <c r="F3">
-        <v>-2.437733822451741</v>
+        <v>-2.6273628599332</v>
       </c>
       <c r="G3">
-        <v>-11.73222362401826</v>
+        <v>-14.51894485315611</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.398067039752939</v>
       </c>
       <c r="E4">
-        <v>-23.02283185881381</v>
+        <v>-26.18561773219896</v>
       </c>
       <c r="F4">
-        <v>-2.564941234295244</v>
+        <v>-2.578103992325728</v>
       </c>
       <c r="G4">
-        <v>-11.70780835066613</v>
+        <v>-14.47011099590632</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.422221603168571</v>
       </c>
       <c r="E5">
-        <v>-23.31491390383454</v>
+        <v>-27.14057327398847</v>
       </c>
       <c r="F5">
-        <v>-2.532529702925908</v>
+        <v>-2.635205842502906</v>
       </c>
       <c r="G5">
-        <v>-11.61085902454858</v>
+        <v>-14.37957916231664</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.444767049251032</v>
       </c>
       <c r="E6">
-        <v>-23.89334041730829</v>
+        <v>-26.8872594949474</v>
       </c>
       <c r="F6">
-        <v>-2.630849458331584</v>
+        <v>-2.728481668792936</v>
       </c>
       <c r="G6">
-        <v>-11.21882753233362</v>
+        <v>-14.15579456022575</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.444885639347454</v>
       </c>
       <c r="E7">
-        <v>-24.6093691419791</v>
+        <v>-28.18931351247683</v>
       </c>
       <c r="F7">
-        <v>-2.506194246456106</v>
+        <v>-2.742852186496702</v>
       </c>
       <c r="G7">
-        <v>-11.09050085559485</v>
+        <v>-14.25765673592359</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.407431287693944</v>
       </c>
       <c r="E8">
-        <v>-24.18825275858381</v>
+        <v>-27.86309130191228</v>
       </c>
       <c r="F8">
-        <v>-2.368131079798915</v>
+        <v>-2.348061394363888</v>
       </c>
       <c r="G8">
-        <v>-10.89168935377946</v>
+        <v>-13.60408552501513</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.316470924957869</v>
       </c>
       <c r="E9">
-        <v>-25.68912942742001</v>
+        <v>-28.55496514622618</v>
       </c>
       <c r="F9">
-        <v>-2.364214558718479</v>
+        <v>-2.421900407914631</v>
       </c>
       <c r="G9">
-        <v>-10.9142937587216</v>
+        <v>-13.60300959771487</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.152165544972007</v>
       </c>
       <c r="E10">
-        <v>-25.45130755795918</v>
+        <v>-28.91544979113277</v>
       </c>
       <c r="F10">
-        <v>-2.503763816496292</v>
+        <v>-2.480031918773489</v>
       </c>
       <c r="G10">
-        <v>-10.56222386171119</v>
+        <v>-13.25377352768607</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.908637011980726</v>
       </c>
       <c r="E11">
-        <v>-26.34295503312146</v>
+        <v>-29.82617799152636</v>
       </c>
       <c r="F11">
-        <v>-2.448085101517123</v>
+        <v>-2.391104192980753</v>
       </c>
       <c r="G11">
-        <v>-10.20673417115871</v>
+        <v>-12.84504695431657</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.585889936431451</v>
       </c>
       <c r="E12">
-        <v>-26.87400465152696</v>
+        <v>-30.13372703952029</v>
       </c>
       <c r="F12">
-        <v>-2.441110247985551</v>
+        <v>-2.406595491780507</v>
       </c>
       <c r="G12">
-        <v>-10.48825303218172</v>
+        <v>-12.8805393130431</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.189063683101289</v>
       </c>
       <c r="E13">
-        <v>-27.50294629255626</v>
+        <v>-30.40197119736465</v>
       </c>
       <c r="F13">
-        <v>-2.565432456165104</v>
+        <v>-2.391602041789836</v>
       </c>
       <c r="G13">
-        <v>-10.18225599744134</v>
+        <v>-12.53248179722628</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.742209080425856</v>
       </c>
       <c r="E14">
-        <v>-28.29878484313826</v>
+        <v>-30.34604001489591</v>
       </c>
       <c r="F14">
-        <v>-2.220606300666948</v>
+        <v>-2.567021264843673</v>
       </c>
       <c r="G14">
-        <v>-9.206750785566458</v>
+        <v>-12.27491804372544</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.271584916765987</v>
       </c>
       <c r="E15">
-        <v>-29.00976431929052</v>
+        <v>-31.82208932498505</v>
       </c>
       <c r="F15">
-        <v>-1.823534184706825</v>
+        <v>-2.113005516880306</v>
       </c>
       <c r="G15">
-        <v>-9.123672645258448</v>
+        <v>-11.36631895719923</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.801302283254544</v>
       </c>
       <c r="E16">
-        <v>-29.81222349887173</v>
+        <v>-31.89711028963312</v>
       </c>
       <c r="F16">
-        <v>-2.028566714043341</v>
+        <v>-2.188664453614999</v>
       </c>
       <c r="G16">
-        <v>-8.736812225175834</v>
+        <v>-10.91209886702907</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.361782718115883</v>
       </c>
       <c r="E17">
-        <v>-30.0997861268328</v>
+        <v>-33.02283232201488</v>
       </c>
       <c r="F17">
-        <v>-1.636516989646391</v>
+        <v>-2.224000121916218</v>
       </c>
       <c r="G17">
-        <v>-8.139437524796506</v>
+        <v>-10.86241751012122</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.973894357170093</v>
       </c>
       <c r="E18">
-        <v>-31.13715989556191</v>
+        <v>-33.41572272692036</v>
       </c>
       <c r="F18">
-        <v>-1.667937793601979</v>
+        <v>-2.10909479437169</v>
       </c>
       <c r="G18">
-        <v>-8.142893734339506</v>
+        <v>-10.35083890793765</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.648048767738424</v>
       </c>
       <c r="E19">
-        <v>-31.57362101313219</v>
+        <v>-34.343597994144</v>
       </c>
       <c r="F19">
-        <v>-1.527083857164757</v>
+        <v>-1.844148935892893</v>
       </c>
       <c r="G19">
-        <v>-7.422363429353749</v>
+        <v>-10.23884646288964</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.394686523849671</v>
       </c>
       <c r="E20">
-        <v>-32.35154265630284</v>
+        <v>-35.26493867337457</v>
       </c>
       <c r="F20">
-        <v>-1.309211633084848</v>
+        <v>-1.658985627079925</v>
       </c>
       <c r="G20">
-        <v>-7.229590362601988</v>
+        <v>-10.40558208897504</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.213150359606059</v>
       </c>
       <c r="E21">
-        <v>-33.28953453445962</v>
+        <v>-35.64077710940417</v>
       </c>
       <c r="F21">
-        <v>-1.386374056655622</v>
+        <v>-1.803297169056433</v>
       </c>
       <c r="G21">
-        <v>-7.413117075662565</v>
+        <v>-10.02396888357217</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.094043998078484</v>
       </c>
       <c r="E22">
-        <v>-33.94893016319051</v>
+        <v>-36.06093345630983</v>
       </c>
       <c r="F22">
-        <v>-1.114882438959903</v>
+        <v>-1.394790269468065</v>
       </c>
       <c r="G22">
-        <v>-7.336570641703537</v>
+        <v>-9.953123209031766</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.030411208476047</v>
       </c>
       <c r="E23">
-        <v>-33.62831420344745</v>
+        <v>-36.82860037009011</v>
       </c>
       <c r="F23">
-        <v>-0.8730985614307839</v>
+        <v>-1.431893673806858</v>
       </c>
       <c r="G23">
-        <v>-7.10348175137453</v>
+        <v>-9.981782601765236</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.010259172488122</v>
       </c>
       <c r="E24">
-        <v>-34.44103264089303</v>
+        <v>-36.73467981917103</v>
       </c>
       <c r="F24">
-        <v>-1.10151258907872</v>
+        <v>-1.094733230254208</v>
       </c>
       <c r="G24">
-        <v>-7.137987567530354</v>
+        <v>-9.839349690483632</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.019257112699746</v>
       </c>
       <c r="E25">
-        <v>-35.22084718619889</v>
+        <v>-37.07787475031633</v>
       </c>
       <c r="F25">
-        <v>-0.6767009339010491</v>
+        <v>-1.035460229114292</v>
       </c>
       <c r="G25">
-        <v>-6.857488354533445</v>
+        <v>-10.19004902164079</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.049562564732122</v>
       </c>
       <c r="E26">
-        <v>-35.11639793321197</v>
+        <v>-37.65263772831787</v>
       </c>
       <c r="F26">
-        <v>-0.7961076099123894</v>
+        <v>-1.050114876837219</v>
       </c>
       <c r="G26">
-        <v>-7.053260775543786</v>
+        <v>-9.934428558371501</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.094728245108735</v>
       </c>
       <c r="E27">
-        <v>-35.11656775098726</v>
+        <v>-37.34817936383418</v>
       </c>
       <c r="F27">
-        <v>-0.5890472371738193</v>
+        <v>-1.143351769859317</v>
       </c>
       <c r="G27">
-        <v>-6.888286359685286</v>
+        <v>-9.993783329345094</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.148670921091047</v>
       </c>
       <c r="E28">
-        <v>-34.2877505884444</v>
+        <v>-37.21244061969126</v>
       </c>
       <c r="F28">
-        <v>-0.8266147246226896</v>
+        <v>-0.8677365392324626</v>
       </c>
       <c r="G28">
-        <v>-6.925986852286506</v>
+        <v>-10.37550578275076</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.210284398557154</v>
       </c>
       <c r="E29">
-        <v>-34.96136788979638</v>
+        <v>-37.70880891990901</v>
       </c>
       <c r="F29">
-        <v>-0.3671831105798194</v>
+        <v>-1.075969051845994</v>
       </c>
       <c r="G29">
-        <v>-7.28344962798039</v>
+        <v>-10.09978037642148</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.281644370731958</v>
       </c>
       <c r="E30">
-        <v>-34.99583410546876</v>
+        <v>-37.19347537054714</v>
       </c>
       <c r="F30">
-        <v>-0.3261557298539655</v>
+        <v>-0.9424213159014633</v>
       </c>
       <c r="G30">
-        <v>-7.028385336361703</v>
+        <v>-10.1137674313249</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.363992056964102</v>
       </c>
       <c r="E31">
-        <v>-34.02711426693293</v>
+        <v>-37.12530145859866</v>
       </c>
       <c r="F31">
-        <v>-0.5472304223130976</v>
+        <v>-0.9173466346187222</v>
       </c>
       <c r="G31">
-        <v>-7.347048518335329</v>
+        <v>-10.48152269310038</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.460567478301027</v>
       </c>
       <c r="E32">
-        <v>-34.23753886864736</v>
+        <v>-36.69915846905486</v>
       </c>
       <c r="F32">
-        <v>-0.5651712035229293</v>
+        <v>-1.047622319322195</v>
       </c>
       <c r="G32">
-        <v>-7.388850776859707</v>
+        <v>-10.53102197000356</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.575977133741692</v>
       </c>
       <c r="E33">
-        <v>-34.25146619045795</v>
+        <v>-36.4219932174154</v>
       </c>
       <c r="F33">
-        <v>-0.5683430223082485</v>
+        <v>-1.039872942269006</v>
       </c>
       <c r="G33">
-        <v>-7.744926433972637</v>
+        <v>-10.33758679414395</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.710678004538549</v>
       </c>
       <c r="E34">
-        <v>-33.68059770010301</v>
+        <v>-35.9473819705675</v>
       </c>
       <c r="F34">
-        <v>-0.5089896695302611</v>
+        <v>-0.8708313198493216</v>
       </c>
       <c r="G34">
-        <v>-8.645798707210192</v>
+        <v>-10.94255588599036</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.865220695713929</v>
       </c>
       <c r="E35">
-        <v>-32.5032420070858</v>
+        <v>-35.82377047981712</v>
       </c>
       <c r="F35">
-        <v>-0.6192105794119578</v>
+        <v>-0.9166764853898575</v>
       </c>
       <c r="G35">
-        <v>-8.459607004990501</v>
+        <v>-11.25958365846759</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.041374775469267</v>
       </c>
       <c r="E36">
-        <v>-32.95851214144693</v>
+        <v>-35.04575373869231</v>
       </c>
       <c r="F36">
-        <v>-0.6115150462399503</v>
+        <v>-1.018793476969966</v>
       </c>
       <c r="G36">
-        <v>-8.267780754262972</v>
+        <v>-11.0327086621158</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.235812725868134</v>
       </c>
       <c r="E37">
-        <v>-31.77635173750758</v>
+        <v>-35.23912637153085</v>
       </c>
       <c r="F37">
-        <v>-0.2609582450492276</v>
+        <v>-0.7729787636588245</v>
       </c>
       <c r="G37">
-        <v>-8.382961254665295</v>
+        <v>-10.96150875920269</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.445978392942242</v>
       </c>
       <c r="E38">
-        <v>-31.95261805978214</v>
+        <v>-34.05150236370125</v>
       </c>
       <c r="F38">
-        <v>-0.4877329336070231</v>
+        <v>-1.003725473913043</v>
       </c>
       <c r="G38">
-        <v>-8.509086418620448</v>
+        <v>-11.14890218945314</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.67248354694305</v>
       </c>
       <c r="E39">
-        <v>-31.22438962613466</v>
+        <v>-33.34952322963923</v>
       </c>
       <c r="F39">
-        <v>-0.3595256823083408</v>
+        <v>-0.7392658670996901</v>
       </c>
       <c r="G39">
-        <v>-8.487329513336357</v>
+        <v>-11.24514636937083</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.911138404013212</v>
       </c>
       <c r="E40">
-        <v>-30.90869838187495</v>
+        <v>-32.99192322267552</v>
       </c>
       <c r="F40">
-        <v>-0.3754104556244241</v>
+        <v>-0.558111028148869</v>
       </c>
       <c r="G40">
-        <v>-8.750428498978858</v>
+        <v>-11.01841372647722</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.159638066809269</v>
       </c>
       <c r="E41">
-        <v>-30.00217034112346</v>
+        <v>-32.85717847857729</v>
       </c>
       <c r="F41">
-        <v>-0.2473382282123981</v>
+        <v>-0.7201123560121599</v>
       </c>
       <c r="G41">
-        <v>-8.759794032309456</v>
+        <v>-10.89994254380886</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.419497503594282</v>
       </c>
       <c r="E42">
-        <v>-29.1742339667751</v>
+        <v>-32.41069131955403</v>
       </c>
       <c r="F42">
-        <v>-0.1031857327772282</v>
+        <v>-0.6577710820122747</v>
       </c>
       <c r="G42">
-        <v>-8.537037354608515</v>
+        <v>-11.32995592499588</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.687324561238728</v>
       </c>
       <c r="E43">
-        <v>-28.75815324647634</v>
+        <v>-31.44260093890527</v>
       </c>
       <c r="F43">
-        <v>0.03342861929246629</v>
+        <v>-0.4287432341188647</v>
       </c>
       <c r="G43">
-        <v>-8.478440698563414</v>
+        <v>-11.78331527332583</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.96186841356212</v>
       </c>
       <c r="E44">
-        <v>-28.56821546117262</v>
+        <v>-31.21805202676093</v>
       </c>
       <c r="F44">
-        <v>-0.06440571281516931</v>
+        <v>-0.3849201134085624</v>
       </c>
       <c r="G44">
-        <v>-8.86519849173431</v>
+        <v>-11.46071916325155</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.246253485341438</v>
       </c>
       <c r="E45">
-        <v>-27.52965976072751</v>
+        <v>-30.75046897157294</v>
       </c>
       <c r="F45">
-        <v>-0.09496418630444307</v>
+        <v>-0.3109104561728434</v>
       </c>
       <c r="G45">
-        <v>-8.546555173033919</v>
+        <v>-11.37208923807418</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.538362692612826</v>
       </c>
       <c r="E46">
-        <v>-27.30568143630813</v>
+        <v>-30.38870729699618</v>
       </c>
       <c r="F46">
-        <v>0.1632834933553168</v>
+        <v>-0.319010232637417</v>
       </c>
       <c r="G46">
-        <v>-9.379475188532393</v>
+        <v>-11.52059368987481</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.839147109890268</v>
       </c>
       <c r="E47">
-        <v>-26.52583745592123</v>
+        <v>-29.54394764170932</v>
       </c>
       <c r="F47">
-        <v>0.1758398864469517</v>
+        <v>-0.6221380298134512</v>
       </c>
       <c r="G47">
-        <v>-8.6370323826222</v>
+        <v>-11.80470139750952</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.153811095039829</v>
       </c>
       <c r="E48">
-        <v>-25.85656975385362</v>
+        <v>-28.64267715928074</v>
       </c>
       <c r="F48">
-        <v>0.380725794753173</v>
+        <v>-0.367527711419384</v>
       </c>
       <c r="G48">
-        <v>-8.755394317287763</v>
+        <v>-11.80311895674175</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.480605510657509</v>
       </c>
       <c r="E49">
-        <v>-25.58836182380132</v>
+        <v>-28.58656936632571</v>
       </c>
       <c r="F49">
-        <v>0.3514719999233085</v>
+        <v>-0.3820904103605993</v>
       </c>
       <c r="G49">
-        <v>-8.747137816712822</v>
+        <v>-11.12779746164028</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.820876119060524</v>
       </c>
       <c r="E50">
-        <v>-24.34307675643205</v>
+        <v>-28.23455749628747</v>
       </c>
       <c r="F50">
-        <v>0.3749081704833121</v>
+        <v>-0.1971822387076937</v>
       </c>
       <c r="G50">
-        <v>-8.829560469004056</v>
+        <v>-11.52017325059132</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.179116927322285</v>
       </c>
       <c r="E51">
-        <v>-24.14977884341464</v>
+        <v>-27.2345798659137</v>
       </c>
       <c r="F51">
-        <v>0.4770160500219904</v>
+        <v>-0.3663646835858535</v>
       </c>
       <c r="G51">
-        <v>-8.78743708756237</v>
+        <v>-11.76553102268887</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.551771953581934</v>
       </c>
       <c r="E52">
-        <v>-23.53736160403933</v>
+        <v>-27.59131040586793</v>
       </c>
       <c r="F52">
-        <v>0.1496402822312089</v>
+        <v>-0.2655987592397104</v>
       </c>
       <c r="G52">
-        <v>-8.676924456370418</v>
+        <v>-11.86249359098858</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.939234064016881</v>
       </c>
       <c r="E53">
-        <v>-22.73470317160178</v>
+        <v>-26.82236193394348</v>
       </c>
       <c r="F53">
-        <v>0.4335300748446275</v>
+        <v>-0.1615947467160241</v>
       </c>
       <c r="G53">
-        <v>-8.830348378842404</v>
+        <v>-11.74704162585204</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.343537712772173</v>
       </c>
       <c r="E54">
-        <v>-22.76062415682168</v>
+        <v>-26.33140289592789</v>
       </c>
       <c r="F54">
-        <v>0.5773214020921769</v>
+        <v>-0.07297268849492181</v>
       </c>
       <c r="G54">
-        <v>-8.94728346838054</v>
+        <v>-11.84117036717013</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.757554854396806</v>
       </c>
       <c r="E55">
-        <v>-22.36761601159201</v>
+        <v>-25.08050704926312</v>
       </c>
       <c r="F55">
-        <v>0.3752196366267647</v>
+        <v>-0.05596630571544795</v>
       </c>
       <c r="G55">
-        <v>-8.869495579844285</v>
+        <v>-12.16054862698024</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.17728769025439</v>
       </c>
       <c r="E56">
-        <v>-21.47752633148837</v>
+        <v>-25.80019930940614</v>
       </c>
       <c r="F56">
-        <v>0.2954892741073123</v>
+        <v>-0.05744742663165347</v>
       </c>
       <c r="G56">
-        <v>-9.116909200721716</v>
+        <v>-11.84867537390766</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.59662267892922</v>
       </c>
       <c r="E57">
-        <v>-21.09510575848862</v>
+        <v>-24.97255728586827</v>
       </c>
       <c r="F57">
-        <v>0.5728225387275728</v>
+        <v>-0.2465463089753218</v>
       </c>
       <c r="G57">
-        <v>-9.188652033103262</v>
+        <v>-12.10910274929997</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.99979091387776</v>
       </c>
       <c r="E58">
-        <v>-20.56227644979811</v>
+        <v>-24.57001217437844</v>
       </c>
       <c r="F58">
-        <v>0.6283380653283901</v>
+        <v>-0.2947390677353914</v>
       </c>
       <c r="G58">
-        <v>-9.111724886407218</v>
+        <v>-12.16209465174708</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.37452009664521</v>
       </c>
       <c r="E59">
-        <v>-20.36186430411465</v>
+        <v>-23.6514112219225</v>
       </c>
       <c r="F59">
-        <v>0.194067282778152</v>
+        <v>-0.3071513248989393</v>
       </c>
       <c r="G59">
-        <v>-9.351209750718096</v>
+        <v>-11.98891008295119</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.70609119342525</v>
       </c>
       <c r="E60">
-        <v>-20.17454850526137</v>
+        <v>-23.93248001815658</v>
       </c>
       <c r="F60">
-        <v>0.3278627005761198</v>
+        <v>-0.1704798154784516</v>
       </c>
       <c r="G60">
-        <v>-9.447434067362552</v>
+        <v>-12.09447344856193</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.97560228669813</v>
       </c>
       <c r="E61">
-        <v>-19.9017441740913</v>
+        <v>-24.20527982085265</v>
       </c>
       <c r="F61">
-        <v>0.1693264335587392</v>
+        <v>-0.2043757812336046</v>
       </c>
       <c r="G61">
-        <v>-8.956953571900751</v>
+        <v>-12.3774059125302</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.17179025199778</v>
       </c>
       <c r="E62">
-        <v>-18.63014414426345</v>
+        <v>-23.53473056064087</v>
       </c>
       <c r="F62">
-        <v>0.2608693152421125</v>
+        <v>-0.4499071928929892</v>
       </c>
       <c r="G62">
-        <v>-9.363703749583305</v>
+        <v>-12.12030232485932</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.28266750469887</v>
       </c>
       <c r="E63">
-        <v>-19.60098557287187</v>
+        <v>-23.49006169302921</v>
       </c>
       <c r="F63">
-        <v>0.1431624491413168</v>
+        <v>-0.2401604246671404</v>
       </c>
       <c r="G63">
-        <v>-9.509817987504578</v>
+        <v>-12.1761909546533</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.29666173550315</v>
       </c>
       <c r="E64">
-        <v>-19.26744081983691</v>
+        <v>-23.38628265419543</v>
       </c>
       <c r="F64">
-        <v>-0.01697919390268922</v>
+        <v>-0.3453523160464412</v>
       </c>
       <c r="G64">
-        <v>-9.335481348861018</v>
+        <v>-12.13612673253704</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.211052220533</v>
       </c>
       <c r="E65">
-        <v>-18.90421644815568</v>
+        <v>-23.72917870605623</v>
       </c>
       <c r="F65">
-        <v>-0.3170768231192829</v>
+        <v>-0.4424220650412929</v>
       </c>
       <c r="G65">
-        <v>-9.521159916522121</v>
+        <v>-12.018019709878</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.02320056085912</v>
       </c>
       <c r="E66">
-        <v>-18.25834284281169</v>
+        <v>-23.22424479725297</v>
       </c>
       <c r="F66">
-        <v>-0.1907491374575527</v>
+        <v>-0.7475371156166432</v>
       </c>
       <c r="G66">
-        <v>-9.503544503707658</v>
+        <v>-12.48513768546916</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.73660468684965</v>
       </c>
       <c r="E67">
-        <v>-19.02706036256175</v>
+        <v>-22.93542325351776</v>
       </c>
       <c r="F67">
-        <v>-0.4333663525938887</v>
+        <v>-0.7998302930205704</v>
       </c>
       <c r="G67">
-        <v>-9.37553563934066</v>
+        <v>-12.47220338404723</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.36564569908967</v>
       </c>
       <c r="E68">
-        <v>-18.36639676110871</v>
+        <v>-23.16666525024544</v>
       </c>
       <c r="F68">
-        <v>-0.3505610902752445</v>
+        <v>-0.9867157776639585</v>
       </c>
       <c r="G68">
-        <v>-9.666016147138471</v>
+        <v>-11.70394825456734</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.92343654427435</v>
       </c>
       <c r="E69">
-        <v>-18.5533638674634</v>
+        <v>-23.02693918473877</v>
       </c>
       <c r="F69">
-        <v>-0.6438810174021327</v>
+        <v>-0.8219750387996095</v>
       </c>
       <c r="G69">
-        <v>-9.037376654686266</v>
+        <v>-12.28944140700623</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.42990018886084</v>
       </c>
       <c r="E70">
-        <v>-18.85131481479807</v>
+        <v>-22.52809607347583</v>
       </c>
       <c r="F70">
-        <v>-0.8042761408713953</v>
+        <v>-1.16454472149254</v>
       </c>
       <c r="G70">
-        <v>-9.086839515588517</v>
+        <v>-11.71962699824133</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.911050849329623</v>
       </c>
       <c r="E71">
-        <v>-18.25935722098941</v>
+        <v>-22.25786391554211</v>
       </c>
       <c r="F71">
-        <v>-0.706494824277539</v>
+        <v>-1.230500990838242</v>
       </c>
       <c r="G71">
-        <v>-8.611564355788587</v>
+        <v>-11.60900842959212</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.386182311207213</v>
       </c>
       <c r="E72">
-        <v>-18.77560778633784</v>
+        <v>-22.77147890901807</v>
       </c>
       <c r="F72">
-        <v>-1.121998943317354</v>
+        <v>-0.9993732315787349</v>
       </c>
       <c r="G72">
-        <v>-9.041647258431926</v>
+        <v>-11.48567736607212</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.878060285849676</v>
       </c>
       <c r="E73">
-        <v>-18.20986100008557</v>
+        <v>-22.47946479110746</v>
       </c>
       <c r="F73">
-        <v>-1.044846460155414</v>
+        <v>-1.31801800694401</v>
       </c>
       <c r="G73">
-        <v>-8.986652475933553</v>
+        <v>-12.16131998409089</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.409391072592891</v>
       </c>
       <c r="E74">
-        <v>-18.15096366714181</v>
+        <v>-22.94274126751415</v>
       </c>
       <c r="F74">
-        <v>-1.300107046960679</v>
+        <v>-1.46823663686988</v>
       </c>
       <c r="G74">
-        <v>-8.584507267096125</v>
+        <v>-11.59556761470268</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.990408248728441</v>
       </c>
       <c r="E75">
-        <v>-18.31395250362588</v>
+        <v>-22.85597117705318</v>
       </c>
       <c r="F75">
-        <v>-1.208940244078176</v>
+        <v>-1.406568825568471</v>
       </c>
       <c r="G75">
-        <v>-8.468767284497664</v>
+        <v>-11.22252872224653</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.631565686712704</v>
       </c>
       <c r="E76">
-        <v>-19.00259754597232</v>
+        <v>-22.91921584504431</v>
       </c>
       <c r="F76">
-        <v>-1.487454760614829</v>
+        <v>-1.599654640221813</v>
       </c>
       <c r="G76">
-        <v>-8.032182470415197</v>
+        <v>-11.09472180115742</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.340296599565797</v>
       </c>
       <c r="E77">
-        <v>-19.22969146050897</v>
+        <v>-22.73669570016515</v>
       </c>
       <c r="F77">
-        <v>-1.627474531077432</v>
+        <v>-1.88221821662335</v>
       </c>
       <c r="G77">
-        <v>-8.189317514436706</v>
+        <v>-11.26050399012751</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.111186693924958</v>
       </c>
       <c r="E78">
-        <v>-18.64334464599581</v>
+        <v>-23.11319755763688</v>
       </c>
       <c r="F78">
-        <v>-1.718996703575735</v>
+        <v>-1.778538924121561</v>
       </c>
       <c r="G78">
-        <v>-7.896923511317195</v>
+        <v>-10.78058082439044</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.940195054171344</v>
       </c>
       <c r="E79">
-        <v>-19.16722116157316</v>
+        <v>-23.8704987944136</v>
       </c>
       <c r="F79">
-        <v>-1.611665967562406</v>
+        <v>-1.946212911959223</v>
       </c>
       <c r="G79">
-        <v>-8.033821190457138</v>
+        <v>-11.25712061258637</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.822875761658736</v>
       </c>
       <c r="E80">
-        <v>-20.60071866564923</v>
+        <v>-23.84532500740496</v>
       </c>
       <c r="F80">
-        <v>-1.712085634334179</v>
+        <v>-1.855077587038027</v>
       </c>
       <c r="G80">
-        <v>-7.474362168139081</v>
+        <v>-10.66323853775097</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.745699398408138</v>
       </c>
       <c r="E81">
-        <v>-20.47623544365237</v>
+        <v>-24.38587989275255</v>
       </c>
       <c r="F81">
-        <v>-1.919765625890043</v>
+        <v>-1.958151342968369</v>
       </c>
       <c r="G81">
-        <v>-7.350938409343973</v>
+        <v>-10.63154337475799</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.699028253227559</v>
       </c>
       <c r="E82">
-        <v>-20.45126996644809</v>
+        <v>-24.1247771384183</v>
       </c>
       <c r="F82">
-        <v>-1.631629621969874</v>
+        <v>-2.212631607680197</v>
       </c>
       <c r="G82">
-        <v>-7.839872880038935</v>
+        <v>-10.88281709173421</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.677262069211913</v>
       </c>
       <c r="E83">
-        <v>-21.12289700347369</v>
+        <v>-25.06747410106904</v>
       </c>
       <c r="F83">
-        <v>-1.981715910475807</v>
+        <v>-2.043681934042224</v>
       </c>
       <c r="G83">
-        <v>-7.319802728547128</v>
+        <v>-10.70902007201355</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.670896114223353</v>
       </c>
       <c r="E84">
-        <v>-21.96061941015263</v>
+        <v>-25.74406434560705</v>
       </c>
       <c r="F84">
-        <v>-2.452884662248943</v>
+        <v>-2.066886990096847</v>
       </c>
       <c r="G84">
-        <v>-7.38293483198103</v>
+        <v>-10.62814344448916</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.676246620009474</v>
       </c>
       <c r="E85">
-        <v>-22.75095586481531</v>
+        <v>-26.192134206296</v>
       </c>
       <c r="F85">
-        <v>-1.966313246988153</v>
+        <v>-2.152071323596331</v>
       </c>
       <c r="G85">
-        <v>-7.12824132146274</v>
+        <v>-10.44783458169275</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.697411879645639</v>
       </c>
       <c r="E86">
-        <v>-23.33677284786957</v>
+        <v>-27.497480424429</v>
       </c>
       <c r="F86">
-        <v>-2.139572916222892</v>
+        <v>-2.366923320125633</v>
       </c>
       <c r="G86">
-        <v>-7.113502772721905</v>
+        <v>-10.6567664212217</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.734442765998155</v>
       </c>
       <c r="E87">
-        <v>-24.96067909854615</v>
+        <v>-28.32731875786059</v>
       </c>
       <c r="F87">
-        <v>-2.174261629582524</v>
+        <v>-2.334474512223171</v>
       </c>
       <c r="G87">
-        <v>-7.256389228742388</v>
+        <v>-10.18832753796037</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.788414319077652</v>
       </c>
       <c r="E88">
-        <v>-25.62342579804272</v>
+        <v>-28.77768002639741</v>
       </c>
       <c r="F88">
-        <v>-2.298887848598904</v>
+        <v>-2.267087652372834</v>
       </c>
       <c r="G88">
-        <v>-7.084916211990298</v>
+        <v>-10.23872728325023</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.867674320985209</v>
       </c>
       <c r="E89">
-        <v>-26.86515148484196</v>
+        <v>-30.11833928484223</v>
       </c>
       <c r="F89">
-        <v>-2.319702236329047</v>
+        <v>-2.518053154194583</v>
       </c>
       <c r="G89">
-        <v>-6.455419288243421</v>
+        <v>-10.51232069825222</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.974514270059016</v>
       </c>
       <c r="E90">
-        <v>-27.92205203349214</v>
+        <v>-31.07995394766002</v>
       </c>
       <c r="F90">
-        <v>-2.132386000636203</v>
+        <v>-2.640147054060605</v>
       </c>
       <c r="G90">
-        <v>-7.129711203682176</v>
+        <v>-10.75245442948879</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.108408732491615</v>
       </c>
       <c r="E91">
-        <v>-29.45748322324387</v>
+        <v>-32.20512577044984</v>
       </c>
       <c r="F91">
-        <v>-2.397763438531859</v>
+        <v>-2.419777302261255</v>
       </c>
       <c r="G91">
-        <v>-6.945972615707086</v>
+        <v>-10.35873455904881</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.274397653457521</v>
       </c>
       <c r="E92">
-        <v>-30.73435666105364</v>
+        <v>-34.00094874411662</v>
       </c>
       <c r="F92">
-        <v>-2.543928866755831</v>
+        <v>-2.888687096126958</v>
       </c>
       <c r="G92">
-        <v>-7.173188598249425</v>
+        <v>-10.68469087284545</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.467730577819098</v>
       </c>
       <c r="E93">
-        <v>-31.74297688407105</v>
+        <v>-34.42877406175427</v>
       </c>
       <c r="F93">
-        <v>-2.660215911128229</v>
+        <v>-2.828094505714382</v>
       </c>
       <c r="G93">
-        <v>-7.771324724102786</v>
+        <v>-11.15349722666164</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.679533621686697</v>
       </c>
       <c r="E94">
-        <v>-33.23222216741854</v>
+        <v>-35.90828765445928</v>
       </c>
       <c r="F94">
-        <v>-2.624974676710929</v>
+        <v>-2.920496404394459</v>
       </c>
       <c r="G94">
-        <v>-7.999464348850581</v>
+        <v>-10.72794646086157</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.907606497082424</v>
       </c>
       <c r="E95">
-        <v>-35.27882750315609</v>
+        <v>-37.39414563924903</v>
       </c>
       <c r="F95">
-        <v>-2.813055495516557</v>
+        <v>-3.00666815183808</v>
       </c>
       <c r="G95">
-        <v>-7.989479743504139</v>
+        <v>-10.64932100430388</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.138523529802649</v>
       </c>
       <c r="E96">
-        <v>-36.79703237778264</v>
+        <v>-39.64714749907118</v>
       </c>
       <c r="F96">
-        <v>-2.991573641024268</v>
+        <v>-3.261898089049442</v>
       </c>
       <c r="G96">
-        <v>-8.024919133502037</v>
+        <v>-10.97277123512729</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.357716959171862</v>
       </c>
       <c r="E97">
-        <v>-38.52891103422411</v>
+        <v>-41.24244964367831</v>
       </c>
       <c r="F97">
-        <v>-3.068555480501231</v>
+        <v>-3.377332743364358</v>
       </c>
       <c r="G97">
-        <v>-8.52720172381134</v>
+        <v>-11.38396085437801</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.557591199390554</v>
       </c>
       <c r="E98">
-        <v>-39.94668114807153</v>
+        <v>-42.45276357052335</v>
       </c>
       <c r="F98">
-        <v>-3.141445185008365</v>
+        <v>-3.392582987249897</v>
       </c>
       <c r="G98">
-        <v>-8.64585167593882</v>
+        <v>-11.51448573335485</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.727246521291811</v>
       </c>
       <c r="E99">
-        <v>-42.46773470559271</v>
+        <v>-44.11628264758203</v>
       </c>
       <c r="F99">
-        <v>-3.161261390018135</v>
+        <v>-3.584191822824048</v>
       </c>
       <c r="G99">
-        <v>-8.601957152633624</v>
+        <v>-11.962677320098</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.85245035736599</v>
       </c>
       <c r="E100">
-        <v>-44.0013114852383</v>
+        <v>-46.27535716377409</v>
       </c>
       <c r="F100">
-        <v>-3.516655856841207</v>
+        <v>-3.620721996920103</v>
       </c>
       <c r="G100">
-        <v>-8.77031494603326</v>
+        <v>-12.28522708253474</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.934046738078262</v>
       </c>
       <c r="E101">
-        <v>-46.38286540095319</v>
+        <v>-48.17631771847694</v>
       </c>
       <c r="F101">
-        <v>-3.416068031486666</v>
+        <v>-4.009333996595435</v>
       </c>
       <c r="G101">
-        <v>-10.0011857091709</v>
+        <v>-12.66485396061404</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.953901647939263</v>
       </c>
       <c r="E102">
-        <v>-48.56864772472397</v>
+        <v>-49.95028174810869</v>
       </c>
       <c r="F102">
-        <v>-3.628985790130431</v>
+        <v>-4.026457179178704</v>
       </c>
       <c r="G102">
-        <v>-9.879685377334113</v>
+        <v>-12.59477964318429</v>
       </c>
     </row>
   </sheetData>
